--- a/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week06_05Oct.xlsx
+++ b/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week06_05Oct.xlsx
@@ -1166,7 +1166,7 @@
     <row r="8" ht="45.75" customHeight="1" s="49">
       <c r="A8" s="57" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: BHM continues.  World Mental Health Day Sat 10 Oct — observe Fri 9; ⚠ handle with care (§8.4: advance flag, opt-out, known-adult check-in).  Launch PSHE W6 (wellbeing &amp; help-seeking) lands exactly this week — deliberate alignment.  Hate Crime Awareness Week may fall this week (tbc).  EVIDENCE: assembly print + EFL: PfA; care protocol logged → log in the SMSC Evidence Tracker.</t>
+          <t>SMSC/BV this week: BHM continues.  World Mental Health Day Sat 10 Oct — observe Fri 9; ⚠ handle with care (§8.4: advance flag, opt-out, known-adult check-in).  Launch PSHE W6 (wellbeing &amp; help-seeking) lands exactly this week — deliberate alignment.  Hate Crime Awareness Week may fall this week (tbc).  EVIDENCE: assembly print + evidence platform: PfA; care protocol logged → log in the SMSC Evidence Tracker.</t>
         </is>
       </c>
       <c r="B8" s="58" t="n"/>
@@ -1476,7 +1476,7 @@
       <c r="I13" s="70" t="inlineStr">
         <is>
           <t>TA plays the receptionist in role-plays; teacher runs the bucket demo theatrically; the wallet cards go home — real transfer to adult life.
-LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to EFL, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
+LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to evidence platform, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
         </is>
       </c>
       <c r="J13" s="70" t="inlineStr">
